--- a/Brief and files/heart failure data catalogue With Data.xlsx
+++ b/Brief and files/heart failure data catalogue With Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noahaslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noahaslan/Desktop/Uni Work/Oxford Brookes/Year 3 Uni work/COMP 6013 Project:Dissertation/Dashboard code folder/Brief and files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6B9646-7265-E144-AFBB-8155B1D1E6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17120" activeTab="1" xr2:uid="{BCC61590-1505-46FA-AFC9-CAD58C82448A}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17120" activeTab="1" xr2:uid="{BCC61590-1505-46FA-AFC9-CAD58C82448A}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="3" r:id="rId1"/>
@@ -4037,6 +4037,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="d4138443-ee6d-4b26-8b57-d94a58805224" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100148D45EC9781F949A0CAA7115F2F2010" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5eb2a6caf9d93b40a01c0cf8a8efce3f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="d4138443-ee6d-4b26-8b57-d94a58805224" xmlns:ns4="8474001e-63e9-4a93-9c01-a8f0bfa29f8b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff2e2e1b8afe4b7b2d66968e54e0e9c4" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4280,26 +4299,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC53B54-5460-44CF-969B-84BEA4BC1063}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8474001e-63e9-4a93-9c01-a8f0bfa29f8b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d4138443-ee6d-4b26-8b57-d94a58805224"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="d4138443-ee6d-4b26-8b57-d94a58805224" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{180FD8C1-991A-498A-9357-2A5B0C5ECE67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32FF6341-1B81-42DC-B813-655E42F9B03A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4317,30 +4343,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{180FD8C1-991A-498A-9357-2A5B0C5ECE67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC53B54-5460-44CF-969B-84BEA4BC1063}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8474001e-63e9-4a93-9c01-a8f0bfa29f8b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d4138443-ee6d-4b26-8b57-d94a58805224"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>